--- a/artfynd/A 29627-2022 artfynd.xlsx
+++ b/artfynd/A 29627-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29627-2022 artfynd.xlsx
+++ b/artfynd/A 29627-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>99223651</v>
       </c>
       <c r="B2" t="n">
-        <v>90560</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99223737</v>
+        <v>99223665</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534826.2959209717</v>
+        <v>534839</v>
       </c>
       <c r="R3" t="n">
-        <v>6430036.071185637</v>
+        <v>6430087</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,19 +847,9 @@
           <t>2022-03-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-03-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99223665</v>
+        <v>99223737</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534839.1317131841</v>
+        <v>534826</v>
       </c>
       <c r="R4" t="n">
-        <v>6430085.989431195</v>
+        <v>6430036</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,19 +948,9 @@
           <t>2022-03-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-03-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29627-2022 artfynd.xlsx
+++ b/artfynd/A 29627-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99223651</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99223665</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99223737</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>